--- a/Docs/CardDesign.xlsx
+++ b/Docs/CardDesign.xlsx
@@ -12179,25 +12179,25 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId55"/>
-    <hyperlink ref="C3" r:id="rId56"/>
-    <hyperlink ref="C4" r:id="rId57"/>
-    <hyperlink ref="C5" r:id="rId58"/>
-    <hyperlink ref="C6" r:id="rId59"/>
-    <hyperlink ref="C7" r:id="rId60"/>
-    <hyperlink ref="C8" r:id="rId61"/>
-    <hyperlink ref="C9" r:id="rId62"/>
-    <hyperlink ref="C10" r:id="rId63"/>
-    <hyperlink ref="C11" r:id="rId64"/>
-    <hyperlink ref="C12" r:id="rId65"/>
-    <hyperlink ref="C13" r:id="rId66"/>
-    <hyperlink ref="C14" r:id="rId67"/>
-    <hyperlink ref="C15" r:id="rId68"/>
-    <hyperlink ref="C16" r:id="rId69"/>
-    <hyperlink ref="C17" r:id="rId70"/>
-    <hyperlink ref="C18" r:id="rId71"/>
-    <hyperlink ref="C19" r:id="rId72"/>
-    <hyperlink ref="C20" r:id="rId73"/>
+    <hyperlink ref="C2" r:id="rId199"/>
+    <hyperlink ref="C3" r:id="rId200"/>
+    <hyperlink ref="C4" r:id="rId201"/>
+    <hyperlink ref="C5" r:id="rId202"/>
+    <hyperlink ref="C6" r:id="rId203"/>
+    <hyperlink ref="C7" r:id="rId204"/>
+    <hyperlink ref="C8" r:id="rId205"/>
+    <hyperlink ref="C9" r:id="rId206"/>
+    <hyperlink ref="C10" r:id="rId207"/>
+    <hyperlink ref="C11" r:id="rId208"/>
+    <hyperlink ref="C12" r:id="rId209"/>
+    <hyperlink ref="C13" r:id="rId210"/>
+    <hyperlink ref="C14" r:id="rId211"/>
+    <hyperlink ref="C15" r:id="rId212"/>
+    <hyperlink ref="C16" r:id="rId213"/>
+    <hyperlink ref="C17" r:id="rId214"/>
+    <hyperlink ref="C18" r:id="rId215"/>
+    <hyperlink ref="C19" r:id="rId216"/>
+    <hyperlink ref="C20" r:id="rId217"/>
   </hyperlinks>
   <headerFooter/>
 </worksheet>
@@ -48302,11 +48302,11 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="P9" r:id="rId41"/>
-    <hyperlink ref="P11" r:id="rId42"/>
-    <hyperlink ref="P22" r:id="rId43"/>
-    <hyperlink ref="P23" r:id="rId44"/>
-    <hyperlink ref="R23" r:id="rId45"/>
+    <hyperlink ref="P9" r:id="rId73"/>
+    <hyperlink ref="P11" r:id="rId74"/>
+    <hyperlink ref="P22" r:id="rId75"/>
+    <hyperlink ref="P23" r:id="rId76"/>
+    <hyperlink ref="R23" r:id="rId77"/>
   </hyperlinks>
   <headerFooter/>
 </worksheet>
@@ -66651,9 +66651,9 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="P20" r:id="rId11"/>
-    <hyperlink ref="P50" r:id="rId12"/>
-    <hyperlink ref="R50" r:id="rId13"/>
+    <hyperlink ref="P20" r:id="rId27"/>
+    <hyperlink ref="P50" r:id="rId28"/>
+    <hyperlink ref="R50" r:id="rId29"/>
   </hyperlinks>
   <headerFooter/>
 </worksheet>
